--- a/Bug Tracker.xlsx
+++ b/Bug Tracker.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Uni Work\Year 3\FMP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Uni Work\Year 3\FMP\ProcGenTool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C89E3674-EFFA-447D-B74E-8E15669160BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97AB2AD5-5A9E-410E-9CC8-DEAB2AEB446A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{96347398-2AC3-4EB9-A82F-8E2B65190871}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="47">
   <si>
     <t>Bug Tracker</t>
   </si>
@@ -168,6 +168,15 @@
   </si>
   <si>
     <t>Floodfill not running</t>
+  </si>
+  <si>
+    <t>Caves messing up next stages</t>
+  </si>
+  <si>
+    <t>Setting tiles to null</t>
+  </si>
+  <si>
+    <t>Set tiles to hollow (transparent) instead of null</t>
   </si>
 </sst>
 </file>
@@ -895,17 +904,27 @@
       <c r="A13" s="1">
         <v>11</v>
       </c>
-      <c r="B13" s="1"/>
+      <c r="B13" s="1" t="s">
+        <v>44</v>
+      </c>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
+      <c r="E13" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
+      <c r="H13" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
-      <c r="K13" s="1"/>
-      <c r="L13" s="1"/>
+      <c r="K13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>46</v>
+      </c>
       <c r="M13" s="1"/>
       <c r="N13" s="1"/>
       <c r="O13" s="1"/>

--- a/Bug Tracker.xlsx
+++ b/Bug Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Uni Work\Year 3\FMP\ProcGenTool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97AB2AD5-5A9E-410E-9CC8-DEAB2AEB446A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FB76808-A26A-4BE2-9F81-123446888FEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{96347398-2AC3-4EB9-A82F-8E2B65190871}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="53">
   <si>
     <t>Bug Tracker</t>
   </si>
@@ -177,6 +177,24 @@
   </si>
   <si>
     <t>Set tiles to hollow (transparent) instead of null</t>
+  </si>
+  <si>
+    <t>List not displaying properly</t>
+  </si>
+  <si>
+    <t>CustomEditorWindow.cs</t>
+  </si>
+  <si>
+    <t>Changed EditorGUI to EditorGUILayout</t>
+  </si>
+  <si>
+    <t>Wrong class call</t>
+  </si>
+  <si>
+    <t>Plus and minus missing</t>
+  </si>
+  <si>
+    <t>Tiles changed from null to hollow</t>
   </si>
 </sst>
 </file>
@@ -894,7 +912,9 @@
       <c r="K12" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="L12" s="1"/>
+      <c r="L12" s="1" t="s">
+        <v>52</v>
+      </c>
       <c r="M12" s="1"/>
       <c r="N12" s="1"/>
       <c r="O12" s="1"/>
@@ -934,17 +954,27 @@
       <c r="A14" s="1">
         <v>12</v>
       </c>
-      <c r="B14" s="1"/>
+      <c r="B14" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
+      <c r="E14" s="1" t="s">
+        <v>50</v>
+      </c>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
+      <c r="H14" s="1" t="s">
+        <v>48</v>
+      </c>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
-      <c r="K14" s="1"/>
-      <c r="L14" s="1"/>
+      <c r="K14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>49</v>
+      </c>
       <c r="M14" s="1"/>
       <c r="N14" s="1"/>
       <c r="O14" s="1"/>
@@ -954,16 +984,22 @@
       <c r="A15" s="1">
         <v>13</v>
       </c>
-      <c r="B15" s="1"/>
+      <c r="B15" s="1" t="s">
+        <v>51</v>
+      </c>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
+      <c r="H15" s="1" t="s">
+        <v>48</v>
+      </c>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
-      <c r="K15" s="1"/>
+      <c r="K15" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
       <c r="N15" s="1"/>

--- a/Bug Tracker.xlsx
+++ b/Bug Tracker.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Uni Work\Year 3\FMP\ProcGenTool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FB76808-A26A-4BE2-9F81-123446888FEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A42AAE0-5A8B-4DC1-9898-64C2354C6F82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{96347398-2AC3-4EB9-A82F-8E2B65190871}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="57">
   <si>
     <t>Bug Tracker</t>
   </si>
@@ -195,6 +195,18 @@
   </si>
   <si>
     <t>Tiles changed from null to hollow</t>
+  </si>
+  <si>
+    <t>Changed DoList() to DoLayoutList()</t>
+  </si>
+  <si>
+    <t>List not displaying</t>
+  </si>
+  <si>
+    <t>List elements displaying below the list</t>
+  </si>
+  <si>
+    <t>Changed EditorGUILayout back to EditorGUI</t>
   </si>
 </sst>
 </file>
@@ -582,15 +594,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1BD1393-822F-435F-8CD2-D264D0B787D6}">
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:Q20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -599,28 +611,29 @@
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="1"/>
+      <c r="F2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="1"/>
       <c r="G2" s="1"/>
-      <c r="H2" s="1" t="s">
+      <c r="H2" s="1"/>
+      <c r="I2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="I2" s="1"/>
       <c r="J2" s="1"/>
-      <c r="K2" s="1" t="s">
+      <c r="K2" s="1"/>
+      <c r="L2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="M2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="M2" s="1"/>
       <c r="N2" s="1"/>
       <c r="O2" s="1"/>
       <c r="P2" s="1"/>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q2" s="1"/>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -629,28 +642,29 @@
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="1"/>
+      <c r="F3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="1"/>
       <c r="G3" s="1"/>
-      <c r="H3" s="1" t="s">
+      <c r="H3" s="1"/>
+      <c r="I3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="I3" s="1"/>
       <c r="J3" s="1"/>
-      <c r="K3" s="1" t="s">
+      <c r="K3" s="1"/>
+      <c r="L3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="M3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="M3" s="1"/>
       <c r="N3" s="1"/>
       <c r="O3" s="1"/>
       <c r="P3" s="1"/>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q3" s="1"/>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -659,28 +673,29 @@
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
-      <c r="E4" s="1" t="s">
+      <c r="E4" s="1"/>
+      <c r="F4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="1"/>
       <c r="G4" s="1"/>
-      <c r="H4" s="1" t="s">
+      <c r="H4" s="1"/>
+      <c r="I4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="1"/>
       <c r="J4" s="1"/>
-      <c r="K4" s="1" t="s">
+      <c r="K4" s="1"/>
+      <c r="L4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="L4" s="1" t="s">
+      <c r="M4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="M4" s="1"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
       <c r="P4" s="1"/>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q4" s="1"/>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -689,28 +704,29 @@
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
-      <c r="E5" s="1" t="s">
+      <c r="E5" s="1"/>
+      <c r="F5" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F5" s="1"/>
       <c r="G5" s="1"/>
-      <c r="H5" s="1" t="s">
+      <c r="H5" s="1"/>
+      <c r="I5" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="I5" s="1"/>
       <c r="J5" s="1"/>
-      <c r="K5" s="1" t="s">
+      <c r="K5" s="1"/>
+      <c r="L5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="L5" s="1" t="s">
+      <c r="M5" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="M5" s="1"/>
       <c r="N5" s="1"/>
       <c r="O5" s="1"/>
       <c r="P5" s="1"/>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q5" s="1"/>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -719,28 +735,29 @@
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
-      <c r="E6" s="1" t="s">
+      <c r="E6" s="1"/>
+      <c r="F6" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F6" s="1"/>
       <c r="G6" s="1"/>
-      <c r="H6" s="1" t="s">
+      <c r="H6" s="1"/>
+      <c r="I6" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="I6" s="1"/>
       <c r="J6" s="1"/>
-      <c r="K6" s="1" t="s">
+      <c r="K6" s="1"/>
+      <c r="L6" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L6" s="1" t="s">
+      <c r="M6" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="M6" s="1"/>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
       <c r="P6" s="1"/>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q6" s="1"/>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -749,28 +766,29 @@
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
-      <c r="E7" s="1" t="s">
+      <c r="E7" s="1"/>
+      <c r="F7" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F7" s="1"/>
       <c r="G7" s="1"/>
-      <c r="H7" s="1" t="s">
+      <c r="H7" s="1"/>
+      <c r="I7" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="I7" s="1"/>
       <c r="J7" s="1"/>
-      <c r="K7" s="1" t="s">
+      <c r="K7" s="1"/>
+      <c r="L7" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="L7" s="1" t="s">
+      <c r="M7" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="M7" s="1"/>
       <c r="N7" s="1"/>
       <c r="O7" s="1"/>
       <c r="P7" s="1"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q7" s="1"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -779,28 +797,29 @@
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
-      <c r="E8" s="1" t="s">
+      <c r="E8" s="1"/>
+      <c r="F8" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="F8" s="1"/>
       <c r="G8" s="1"/>
-      <c r="H8" s="1" t="s">
+      <c r="H8" s="1"/>
+      <c r="I8" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="I8" s="1"/>
       <c r="J8" s="1"/>
-      <c r="K8" s="1" t="s">
+      <c r="K8" s="1"/>
+      <c r="L8" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L8" s="1" t="s">
+      <c r="M8" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="M8" s="1"/>
       <c r="N8" s="1"/>
       <c r="O8" s="1"/>
       <c r="P8" s="1"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q8" s="1"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -809,28 +828,29 @@
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
-      <c r="E9" s="1" t="s">
+      <c r="E9" s="1"/>
+      <c r="F9" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F9" s="1"/>
       <c r="G9" s="1"/>
-      <c r="H9" s="1" t="s">
+      <c r="H9" s="1"/>
+      <c r="I9" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="I9" s="1"/>
       <c r="J9" s="1"/>
-      <c r="K9" s="1" t="s">
+      <c r="K9" s="1"/>
+      <c r="L9" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L9" s="1" t="s">
+      <c r="M9" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="M9" s="1"/>
       <c r="N9" s="1"/>
       <c r="O9" s="1"/>
       <c r="P9" s="1"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q9" s="1"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -839,28 +859,29 @@
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
-      <c r="E10" s="1" t="s">
+      <c r="E10" s="1"/>
+      <c r="F10" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="F10" s="1"/>
       <c r="G10" s="1"/>
-      <c r="H10" s="1" t="s">
+      <c r="H10" s="1"/>
+      <c r="I10" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="I10" s="1"/>
       <c r="J10" s="1"/>
-      <c r="K10" s="1" t="s">
+      <c r="K10" s="1"/>
+      <c r="L10" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L10" s="1" t="s">
+      <c r="M10" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="M10" s="1"/>
       <c r="N10" s="1"/>
       <c r="O10" s="1"/>
       <c r="P10" s="1"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q10" s="1"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -869,28 +890,29 @@
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
-      <c r="E11" s="1" t="s">
+      <c r="E11" s="1"/>
+      <c r="F11" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="F11" s="1"/>
       <c r="G11" s="1"/>
-      <c r="H11" s="1" t="s">
+      <c r="H11" s="1"/>
+      <c r="I11" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="I11" s="1"/>
       <c r="J11" s="1"/>
-      <c r="K11" s="1" t="s">
+      <c r="K11" s="1"/>
+      <c r="L11" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L11" s="1" t="s">
+      <c r="M11" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="M11" s="1"/>
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
       <c r="P11" s="1"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q11" s="1"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -899,28 +921,29 @@
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
-      <c r="E12" s="1" t="s">
+      <c r="E12" s="1"/>
+      <c r="F12" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="F12" s="1"/>
       <c r="G12" s="1"/>
-      <c r="H12" s="1" t="s">
+      <c r="H12" s="1"/>
+      <c r="I12" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="I12" s="1"/>
       <c r="J12" s="1"/>
-      <c r="K12" s="1" t="s">
+      <c r="K12" s="1"/>
+      <c r="L12" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="L12" s="1" t="s">
+      <c r="M12" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="M12" s="1"/>
       <c r="N12" s="1"/>
       <c r="O12" s="1"/>
       <c r="P12" s="1"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q12" s="1"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>11</v>
       </c>
@@ -929,28 +952,29 @@
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
-      <c r="E13" s="1" t="s">
+      <c r="E13" s="1"/>
+      <c r="F13" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="F13" s="1"/>
       <c r="G13" s="1"/>
-      <c r="H13" s="1" t="s">
+      <c r="H13" s="1"/>
+      <c r="I13" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="I13" s="1"/>
       <c r="J13" s="1"/>
-      <c r="K13" s="1" t="s">
+      <c r="K13" s="1"/>
+      <c r="L13" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L13" s="1" t="s">
+      <c r="M13" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="M13" s="1"/>
       <c r="N13" s="1"/>
       <c r="O13" s="1"/>
       <c r="P13" s="1"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q13" s="1"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>12</v>
       </c>
@@ -959,28 +983,29 @@
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
-      <c r="E14" s="1" t="s">
+      <c r="E14" s="1"/>
+      <c r="F14" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="F14" s="1"/>
       <c r="G14" s="1"/>
-      <c r="H14" s="1" t="s">
+      <c r="H14" s="1"/>
+      <c r="I14" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="I14" s="1"/>
       <c r="J14" s="1"/>
-      <c r="K14" s="1" t="s">
+      <c r="K14" s="1"/>
+      <c r="L14" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="L14" s="1" t="s">
+      <c r="M14" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="M14" s="1"/>
       <c r="N14" s="1"/>
       <c r="O14" s="1"/>
       <c r="P14" s="1"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q14" s="1"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>13</v>
       </c>
@@ -990,43 +1015,57 @@
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
+      <c r="F15" s="1" t="s">
+        <v>54</v>
+      </c>
       <c r="G15" s="1"/>
-      <c r="H15" s="1" t="s">
+      <c r="H15" s="1"/>
+      <c r="I15" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="I15" s="1"/>
       <c r="J15" s="1"/>
-      <c r="K15" s="1" t="s">
+      <c r="K15" s="1"/>
+      <c r="L15" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L15" s="1"/>
-      <c r="M15" s="1"/>
+      <c r="M15" s="1" t="s">
+        <v>53</v>
+      </c>
       <c r="N15" s="1"/>
       <c r="O15" s="1"/>
       <c r="P15" s="1"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q15" s="1"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>14</v>
       </c>
-      <c r="B16" s="1"/>
+      <c r="B16" s="1" t="s">
+        <v>55</v>
+      </c>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
-      <c r="I16" s="1"/>
+      <c r="I16" s="1" t="s">
+        <v>48</v>
+      </c>
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
-      <c r="L16" s="1"/>
-      <c r="M16" s="1"/>
+      <c r="L16" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="M16" s="1" t="s">
+        <v>56</v>
+      </c>
       <c r="N16" s="1"/>
       <c r="O16" s="1"/>
       <c r="P16" s="1"/>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q16" s="1"/>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>15</v>
       </c>
@@ -1045,8 +1084,9 @@
       <c r="N17" s="1"/>
       <c r="O17" s="1"/>
       <c r="P17" s="1"/>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q17" s="1"/>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>16</v>
       </c>
@@ -1065,8 +1105,9 @@
       <c r="N18" s="1"/>
       <c r="O18" s="1"/>
       <c r="P18" s="1"/>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q18" s="1"/>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>17</v>
       </c>
@@ -1085,8 +1126,9 @@
       <c r="N19" s="1"/>
       <c r="O19" s="1"/>
       <c r="P19" s="1"/>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q19" s="1"/>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>18</v>
       </c>
@@ -1105,6 +1147,7 @@
       <c r="N20" s="1"/>
       <c r="O20" s="1"/>
       <c r="P20" s="1"/>
+      <c r="Q20" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Bug Tracker.xlsx
+++ b/Bug Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Uni Work\Year 3\FMP\ProcGenTool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A42AAE0-5A8B-4DC1-9898-64C2354C6F82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8179935-3FD2-4BBF-8D40-E8EA0014CA98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{96347398-2AC3-4EB9-A82F-8E2B65190871}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="60">
   <si>
     <t>Bug Tracker</t>
   </si>
@@ -207,6 +207,15 @@
   </si>
   <si>
     <t>Changed EditorGUILayout back to EditorGUI</t>
+  </si>
+  <si>
+    <t>Caves throwing error</t>
+  </si>
+  <si>
+    <t>Cave size being negative</t>
+  </si>
+  <si>
+    <t>Added extra checks to ensure no negative numbers</t>
   </si>
 </sst>
 </file>
@@ -1046,7 +1055,9 @@
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
+      <c r="F16" s="1" t="s">
+        <v>50</v>
+      </c>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
       <c r="I16" s="1" t="s">
@@ -1069,18 +1080,28 @@
       <c r="A17" s="1">
         <v>15</v>
       </c>
-      <c r="B17" s="1"/>
+      <c r="B17" s="1" t="s">
+        <v>57</v>
+      </c>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
+      <c r="F17" s="1" t="s">
+        <v>58</v>
+      </c>
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
-      <c r="I17" s="1"/>
+      <c r="I17" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
-      <c r="L17" s="1"/>
-      <c r="M17" s="1"/>
+      <c r="L17" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M17" s="1" t="s">
+        <v>59</v>
+      </c>
       <c r="N17" s="1"/>
       <c r="O17" s="1"/>
       <c r="P17" s="1"/>

--- a/Bug Tracker.xlsx
+++ b/Bug Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Uni Work\Year 3\FMP\ProcGenTool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8179935-3FD2-4BBF-8D40-E8EA0014CA98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DDE712C-7B19-471B-AD48-855A09694C2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{96347398-2AC3-4EB9-A82F-8E2B65190871}"/>
   </bookViews>
